--- a/Team-Data/2020-21/1-17-2020-21.xlsx
+++ b/Team-Data/2020-21/1-17-2020-21.xlsx
@@ -806,16 +806,16 @@
         <v>1.2</v>
       </c>
       <c r="AD2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF2" t="n">
         <v>17</v>
       </c>
-      <c r="AE2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>16</v>
-      </c>
       <c r="AG2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH2" t="n">
         <v>19</v>
@@ -830,7 +830,7 @@
         <v>29</v>
       </c>
       <c r="AL2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM2" t="n">
         <v>11</v>
@@ -872,13 +872,13 @@
         <v>23</v>
       </c>
       <c r="AZ2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA2" t="n">
         <v>13</v>
       </c>
       <c r="BB2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -910,160 +910,160 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>8</v>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.667</v>
+        <v>0.727</v>
       </c>
       <c r="H3" t="n">
         <v>48</v>
       </c>
       <c r="I3" t="n">
-        <v>41.3</v>
+        <v>42.8</v>
       </c>
       <c r="J3" t="n">
-        <v>88.3</v>
+        <v>88.7</v>
       </c>
       <c r="K3" t="n">
-        <v>0.468</v>
+        <v>0.483</v>
       </c>
       <c r="L3" t="n">
-        <v>12.2</v>
+        <v>12.6</v>
       </c>
       <c r="M3" t="n">
-        <v>33.3</v>
+        <v>32.1</v>
       </c>
       <c r="N3" t="n">
-        <v>0.366</v>
+        <v>0.394</v>
       </c>
       <c r="O3" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="P3" t="n">
-        <v>21.3</v>
+        <v>20.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.746</v>
+        <v>0.762</v>
       </c>
       <c r="R3" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="S3" t="n">
-        <v>33.7</v>
+        <v>34.1</v>
       </c>
       <c r="T3" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
       <c r="U3" t="n">
-        <v>22.7</v>
+        <v>23.4</v>
       </c>
       <c r="V3" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="W3" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="AB3" t="n">
-        <v>110.8</v>
+        <v>114</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.3</v>
+        <v>4.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="n">
         <v>2</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>5</v>
       </c>
       <c r="AH3" t="n">
         <v>19</v>
       </c>
       <c r="AI3" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="AJ3" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK3" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="AL3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM3" t="n">
         <v>22</v>
       </c>
       <c r="AN3" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="AO3" t="n">
         <v>22</v>
       </c>
       <c r="AP3" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ3" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AS3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AV3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
         <v>6</v>
       </c>
       <c r="AX3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="BB3" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -1173,52 +1173,52 @@
         <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
         <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ4" t="n">
         <v>21</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL4" t="n">
         <v>6</v>
       </c>
       <c r="AM4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN4" t="n">
         <v>3</v>
       </c>
       <c r="AO4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP4" t="n">
         <v>9</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AR4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS4" t="n">
         <v>4</v>
       </c>
       <c r="AT4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU4" t="n">
         <v>8</v>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
         <v>27</v>
       </c>
       <c r="AJ5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK5" t="n">
         <v>21</v>
@@ -1379,10 +1379,10 @@
         <v>12</v>
       </c>
       <c r="AM5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AN5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO5" t="n">
         <v>17</v>
@@ -1391,13 +1391,13 @@
         <v>14</v>
       </c>
       <c r="AQ5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR5" t="n">
         <v>9</v>
       </c>
       <c r="AS5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT5" t="n">
         <v>16</v>
@@ -1406,13 +1406,13 @@
         <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW5" t="n">
         <v>4</v>
       </c>
       <c r="AX5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
         <v>22</v>
@@ -1421,10 +1421,10 @@
         <v>9</v>
       </c>
       <c r="BA5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
         <v>15</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -1456,142 +1456,142 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.385</v>
+        <v>0.333</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="J6" t="n">
-        <v>87.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.479</v>
+        <v>0.476</v>
       </c>
       <c r="L6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="M6" t="n">
-        <v>35.5</v>
+        <v>36.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.38</v>
+        <v>0.385</v>
       </c>
       <c r="O6" t="n">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="P6" t="n">
-        <v>24.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.799</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="S6" t="n">
-        <v>36.5</v>
+        <v>36</v>
       </c>
       <c r="T6" t="n">
-        <v>44.6</v>
+        <v>44.4</v>
       </c>
       <c r="U6" t="n">
-        <v>25.6</v>
+        <v>25.1</v>
       </c>
       <c r="V6" t="n">
-        <v>18</v>
+        <v>18.3</v>
       </c>
       <c r="W6" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="X6" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z6" t="n">
         <v>21.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AB6" t="n">
         <v>116.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>-3.2</v>
+        <v>-4.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF6" t="n">
         <v>23</v>
       </c>
       <c r="AG6" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AH6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AM6" t="n">
         <v>12</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>8</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>15</v>
       </c>
       <c r="AN6" t="n">
         <v>8</v>
       </c>
       <c r="AO6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AP6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AR6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AV6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW6" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AX6" t="n">
         <v>25</v>
@@ -1603,13 +1603,13 @@
         <v>27</v>
       </c>
       <c r="BA6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB6" t="n">
         <v>4</v>
       </c>
       <c r="BC6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -1716,37 +1716,37 @@
         <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>12</v>
       </c>
       <c r="AF7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
         <v>29</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK7" t="n">
         <v>23</v>
       </c>
       <c r="AL7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM7" t="n">
         <v>29</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
         <v>28</v>
@@ -1758,7 +1758,7 @@
         <v>30</v>
       </c>
       <c r="AR7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS7" t="n">
         <v>27</v>
@@ -1770,28 +1770,28 @@
         <v>20</v>
       </c>
       <c r="AV7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW7" t="n">
         <v>2</v>
       </c>
       <c r="AX7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ7" t="n">
         <v>7</v>
       </c>
       <c r="BA7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB7" t="n">
         <v>30</v>
       </c>
       <c r="BC7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -1820,161 +1820,161 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5</v>
+        <v>0.545</v>
       </c>
       <c r="H8" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I8" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="L8" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="M8" t="n">
         <v>39.3</v>
       </c>
-      <c r="J8" t="n">
-        <v>86.90000000000001</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0.452</v>
-      </c>
-      <c r="L8" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>38.6</v>
-      </c>
       <c r="N8" t="n">
-        <v>0.343</v>
+        <v>0.35</v>
       </c>
       <c r="O8" t="n">
-        <v>16.9</v>
+        <v>17.5</v>
       </c>
       <c r="P8" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.728</v>
+        <v>0.738</v>
       </c>
       <c r="R8" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="S8" t="n">
-        <v>36.1</v>
+        <v>36.2</v>
       </c>
       <c r="T8" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
       <c r="U8" t="n">
-        <v>22.1</v>
+        <v>22.5</v>
       </c>
       <c r="V8" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="W8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="X8" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>108.7</v>
+        <v>109.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
         <v>12</v>
       </c>
       <c r="AF8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AI8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK8" t="n">
         <v>17</v>
       </c>
       <c r="AL8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AM8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AN8" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO8" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AP8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AR8" t="n">
         <v>22</v>
       </c>
       <c r="AS8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV8" t="n">
         <v>4</v>
       </c>
       <c r="AW8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY8" t="n">
         <v>3</v>
       </c>
       <c r="AZ8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC8" t="n">
         <v>6</v>
       </c>
-      <c r="BB8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>10</v>
-      </c>
       <c r="BD8" t="n">
         <v>10</v>
       </c>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -2002,94 +2002,94 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.462</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
         <v>48.8</v>
       </c>
       <c r="I9" t="n">
-        <v>42.8</v>
+        <v>43.1</v>
       </c>
       <c r="J9" t="n">
-        <v>88.7</v>
+        <v>87.8</v>
       </c>
       <c r="K9" t="n">
-        <v>0.483</v>
+        <v>0.491</v>
       </c>
       <c r="L9" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="M9" t="n">
-        <v>34.3</v>
+        <v>34.1</v>
       </c>
       <c r="N9" t="n">
         <v>0.377</v>
       </c>
       <c r="O9" t="n">
-        <v>16.8</v>
+        <v>17.3</v>
       </c>
       <c r="P9" t="n">
-        <v>22.7</v>
+        <v>23.3</v>
       </c>
       <c r="Q9" t="n">
         <v>0.739</v>
       </c>
       <c r="R9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="S9" t="n">
-        <v>32.2</v>
+        <v>32.4</v>
       </c>
       <c r="T9" t="n">
-        <v>43.2</v>
+        <v>42.4</v>
       </c>
       <c r="U9" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="V9" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="W9" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="X9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>115.4</v>
+        <v>116.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE9" t="n">
         <v>12</v>
       </c>
       <c r="AF9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AH9" t="n">
         <v>2</v>
@@ -2098,10 +2098,10 @@
         <v>5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AK9" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AL9" t="n">
         <v>16</v>
@@ -2110,52 +2110,52 @@
         <v>18</v>
       </c>
       <c r="AN9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AP9" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AQ9" t="n">
         <v>21</v>
       </c>
       <c r="AR9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AS9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT9" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AU9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AW9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AX9" t="n">
         <v>24</v>
       </c>
       <c r="AY9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ9" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA9" t="n">
         <v>1</v>
       </c>
       <c r="BB9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -2229,16 +2229,16 @@
         <v>11.2</v>
       </c>
       <c r="S10" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T10" t="n">
-        <v>43.6</v>
+        <v>43.7</v>
       </c>
       <c r="U10" t="n">
         <v>24.6</v>
       </c>
       <c r="V10" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W10" t="n">
         <v>8.4</v>
@@ -2262,13 +2262,13 @@
         <v>-4.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE10" t="n">
         <v>28</v>
       </c>
       <c r="AF10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG10" t="n">
         <v>30</v>
@@ -2286,16 +2286,16 @@
         <v>30</v>
       </c>
       <c r="AL10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP10" t="n">
         <v>15</v>
@@ -2316,28 +2316,28 @@
         <v>18</v>
       </c>
       <c r="AV10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AW10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA10" t="n">
         <v>9</v>
       </c>
-      <c r="AX10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>27</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>8</v>
-      </c>
       <c r="BB10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -2444,16 +2444,16 @@
         <v>-4</v>
       </c>
       <c r="AD11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE11" t="n">
         <v>12</v>
       </c>
       <c r="AF11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
         <v>19</v>
@@ -2468,7 +2468,7 @@
         <v>26</v>
       </c>
       <c r="AL11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM11" t="n">
         <v>9</v>
@@ -2486,7 +2486,7 @@
         <v>10</v>
       </c>
       <c r="AR11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS11" t="n">
         <v>12</v>
@@ -2504,10 +2504,10 @@
         <v>16</v>
       </c>
       <c r="AX11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ11" t="n">
         <v>29</v>
@@ -2516,10 +2516,10 @@
         <v>5</v>
       </c>
       <c r="BB11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC11" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -2626,16 +2626,16 @@
         <v>-2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE12" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH12" t="n">
         <v>4</v>
@@ -2656,40 +2656,40 @@
         <v>10</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ12" t="n">
         <v>20</v>
       </c>
       <c r="AR12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT12" t="n">
         <v>21</v>
       </c>
       <c r="AU12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV12" t="n">
         <v>25</v>
       </c>
       <c r="AW12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AX12" t="n">
         <v>2</v>
       </c>
       <c r="AY12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AZ12" t="n">
         <v>12</v>
@@ -2698,7 +2698,7 @@
         <v>12</v>
       </c>
       <c r="BB12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC12" t="n">
         <v>20</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -2730,160 +2730,160 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>8</v>
       </c>
       <c r="F13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>0.615</v>
+        <v>0.667</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>43.1</v>
+        <v>43.6</v>
       </c>
       <c r="J13" t="n">
-        <v>90</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.479</v>
+        <v>0.484</v>
       </c>
       <c r="L13" t="n">
         <v>11.8</v>
       </c>
       <c r="M13" t="n">
-        <v>33.5</v>
+        <v>33.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.351</v>
+        <v>0.357</v>
       </c>
       <c r="O13" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="P13" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.747</v>
+        <v>0.751</v>
       </c>
       <c r="R13" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="S13" t="n">
-        <v>33.9</v>
+        <v>34.5</v>
       </c>
       <c r="T13" t="n">
-        <v>42.3</v>
+        <v>43.1</v>
       </c>
       <c r="U13" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="V13" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="W13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="X13" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA13" t="n">
         <v>19.4</v>
       </c>
       <c r="AB13" t="n">
-        <v>112.9</v>
+        <v>114.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF13" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AG13" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AH13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ13" t="n">
         <v>9</v>
       </c>
       <c r="AK13" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AL13" t="n">
         <v>22</v>
       </c>
       <c r="AM13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ13" t="n">
         <v>18</v>
       </c>
       <c r="AR13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT13" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AU13" t="n">
         <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW13" t="n">
         <v>3</v>
       </c>
       <c r="AX13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ13" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="BA13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BC13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -2912,106 +2912,106 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F14" t="n">
         <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>0.714</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>41.2</v>
+        <v>40.7</v>
       </c>
       <c r="J14" t="n">
-        <v>84.7</v>
+        <v>84.5</v>
       </c>
       <c r="K14" t="n">
-        <v>0.487</v>
+        <v>0.481</v>
       </c>
       <c r="L14" t="n">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="M14" t="n">
-        <v>35.1</v>
+        <v>34.8</v>
       </c>
       <c r="N14" t="n">
-        <v>0.44</v>
+        <v>0.436</v>
       </c>
       <c r="O14" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="P14" t="n">
         <v>20.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.829</v>
+        <v>0.839</v>
       </c>
       <c r="R14" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>32.8</v>
+        <v>32</v>
       </c>
       <c r="T14" t="n">
-        <v>41.9</v>
+        <v>41.2</v>
       </c>
       <c r="U14" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="V14" t="n">
-        <v>14.1</v>
+        <v>13.8</v>
       </c>
       <c r="W14" t="n">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="X14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y14" t="n">
         <v>2.8</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA14" t="n">
         <v>18.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>114.9</v>
+        <v>113.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH14" t="n">
         <v>19</v>
       </c>
       <c r="AI14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AL14" t="n">
         <v>5</v>
@@ -3023,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="AO14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP14" t="n">
         <v>21</v>
@@ -3035,37 +3035,37 @@
         <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="AT14" t="n">
         <v>30</v>
       </c>
       <c r="AU14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AX14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BA14" t="n">
         <v>29</v>
       </c>
       <c r="BB14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BC14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -3187,13 +3187,13 @@
         <v>19</v>
       </c>
       <c r="AI15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL15" t="n">
         <v>18</v>
@@ -3202,7 +3202,7 @@
         <v>23</v>
       </c>
       <c r="AN15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO15" t="n">
         <v>18</v>
@@ -3211,10 +3211,10 @@
         <v>16</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS15" t="n">
         <v>2</v>
@@ -3229,7 +3229,7 @@
         <v>18</v>
       </c>
       <c r="AW15" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX15" t="n">
         <v>3</v>
@@ -3244,7 +3244,7 @@
         <v>15</v>
       </c>
       <c r="BB15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC15" t="n">
         <v>1</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -3294,10 +3294,10 @@
         <v>41.7</v>
       </c>
       <c r="J16" t="n">
-        <v>92.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.449</v>
+        <v>0.448</v>
       </c>
       <c r="L16" t="n">
         <v>10</v>
@@ -3318,7 +3318,7 @@
         <v>0.767</v>
       </c>
       <c r="R16" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S16" t="n">
         <v>35.1</v>
@@ -3354,19 +3354,19 @@
         <v>-1.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>12</v>
       </c>
       <c r="AF16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI16" t="n">
         <v>11</v>
@@ -3381,10 +3381,10 @@
         <v>27</v>
       </c>
       <c r="AM16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
@@ -3396,13 +3396,13 @@
         <v>12</v>
       </c>
       <c r="AR16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
         <v>4</v>
@@ -3426,10 +3426,10 @@
         <v>30</v>
       </c>
       <c r="BB16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC16" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -3536,16 +3536,16 @@
         <v>-4.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH17" t="n">
         <v>4</v>
@@ -3557,13 +3557,13 @@
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AL17" t="n">
         <v>13</v>
       </c>
       <c r="AM17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN17" t="n">
         <v>16</v>
@@ -3572,7 +3572,7 @@
         <v>8</v>
       </c>
       <c r="AP17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ17" t="n">
         <v>13</v>
@@ -3581,16 +3581,16 @@
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT17" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU17" t="n">
         <v>5</v>
       </c>
       <c r="AV17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW17" t="n">
         <v>26</v>
@@ -3602,7 +3602,7 @@
         <v>4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA17" t="n">
         <v>4</v>
@@ -3611,7 +3611,7 @@
         <v>19</v>
       </c>
       <c r="BC17" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -3718,13 +3718,13 @@
         <v>10.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF18" t="n">
         <v>3</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2</v>
       </c>
       <c r="AG18" t="n">
         <v>3</v>
@@ -3739,7 +3739,7 @@
         <v>8</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL18" t="n">
         <v>2</v>
@@ -3757,7 +3757,7 @@
         <v>22</v>
       </c>
       <c r="AQ18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR18" t="n">
         <v>9</v>
@@ -3787,7 +3787,7 @@
         <v>10</v>
       </c>
       <c r="BA18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
         <v>2</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
         <v>-10.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE19" t="n">
         <v>28</v>
@@ -3930,7 +3930,7 @@
         <v>17</v>
       </c>
       <c r="AN19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO19" t="n">
         <v>20</v>
@@ -3939,7 +3939,7 @@
         <v>17</v>
       </c>
       <c r="AQ19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR19" t="n">
         <v>2</v>
@@ -3954,7 +3954,7 @@
         <v>21</v>
       </c>
       <c r="AV19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW19" t="n">
         <v>17</v>
@@ -3966,10 +3966,10 @@
         <v>17</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB19" t="n">
         <v>23</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -4004,97 +4004,97 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
         <v>7</v>
       </c>
       <c r="G20" t="n">
-        <v>0.417</v>
+        <v>0.364</v>
       </c>
       <c r="H20" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I20" t="n">
-        <v>39.9</v>
+        <v>39.5</v>
       </c>
       <c r="J20" t="n">
         <v>85.8</v>
       </c>
       <c r="K20" t="n">
-        <v>0.466</v>
+        <v>0.46</v>
       </c>
       <c r="L20" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="M20" t="n">
-        <v>30.4</v>
+        <v>31.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.334</v>
+        <v>0.324</v>
       </c>
       <c r="O20" t="n">
-        <v>17.8</v>
+        <v>16.9</v>
       </c>
       <c r="P20" t="n">
-        <v>24.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.717</v>
+        <v>0.707</v>
       </c>
       <c r="R20" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="S20" t="n">
-        <v>36.8</v>
+        <v>37</v>
       </c>
       <c r="T20" t="n">
         <v>48.3</v>
       </c>
       <c r="U20" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V20" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="W20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="X20" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Y20" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>17.6</v>
+        <v>17.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>107.8</v>
+        <v>105.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="AD20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF20" t="n">
         <v>17</v>
       </c>
-      <c r="AE20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>16</v>
-      </c>
       <c r="AG20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH20" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AI20" t="n">
         <v>19</v>
@@ -4109,22 +4109,22 @@
         <v>26</v>
       </c>
       <c r="AM20" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AN20" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AO20" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AP20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ20" t="n">
         <v>28</v>
       </c>
       <c r="AR20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS20" t="n">
         <v>8</v>
@@ -4133,31 +4133,31 @@
         <v>4</v>
       </c>
       <c r="AU20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV20" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW20" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AX20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB20" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BC20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -4186,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F21" t="n">
         <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>0.429</v>
+        <v>0.385</v>
       </c>
       <c r="H21" t="n">
         <v>48</v>
@@ -4204,76 +4204,76 @@
         <v>38.2</v>
       </c>
       <c r="J21" t="n">
-        <v>84.7</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.451</v>
+        <v>0.449</v>
       </c>
       <c r="L21" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="M21" t="n">
-        <v>27.4</v>
+        <v>27.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0.354</v>
+        <v>0.351</v>
       </c>
       <c r="O21" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="P21" t="n">
         <v>20.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.752</v>
+        <v>0.747</v>
       </c>
       <c r="R21" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S21" t="n">
-        <v>35.6</v>
+        <v>35.1</v>
       </c>
       <c r="T21" t="n">
-        <v>46.1</v>
+        <v>45.5</v>
       </c>
       <c r="U21" t="n">
         <v>22</v>
       </c>
       <c r="V21" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="W21" t="n">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="X21" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>20.8</v>
+        <v>20.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="AB21" t="n">
-        <v>101.3</v>
+        <v>101</v>
       </c>
       <c r="AC21" t="n">
-        <v>-2.8</v>
+        <v>-5.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="AF21" t="n">
         <v>23</v>
       </c>
       <c r="AG21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AH21" t="n">
         <v>19</v>
@@ -4294,25 +4294,25 @@
         <v>30</v>
       </c>
       <c r="AN21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AO21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP21" t="n">
         <v>25</v>
       </c>
-      <c r="AP21" t="n">
-        <v>24</v>
-      </c>
       <c r="AQ21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AR21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS21" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AT21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AU21" t="n">
         <v>28</v>
@@ -4321,16 +4321,16 @@
         <v>20</v>
       </c>
       <c r="AW21" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AX21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY21" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AZ21" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
         <v>23</v>
@@ -4339,7 +4339,7 @@
         <v>29</v>
       </c>
       <c r="BC21" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -4446,19 +4446,19 @@
         <v>-6.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
         <v>12</v>
       </c>
       <c r="AF22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AI22" t="n">
         <v>27</v>
@@ -4470,22 +4470,22 @@
         <v>20</v>
       </c>
       <c r="AL22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO22" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR22" t="n">
         <v>29</v>
@@ -4494,13 +4494,13 @@
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AU22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AV22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW22" t="n">
         <v>25</v>
@@ -4515,10 +4515,10 @@
         <v>11</v>
       </c>
       <c r="BA22" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BB22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC22" t="n">
         <v>27</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -4628,16 +4628,16 @@
         <v>-6.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>12</v>
       </c>
       <c r="AF23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH23" t="n">
         <v>19</v>
@@ -4655,7 +4655,7 @@
         <v>28</v>
       </c>
       <c r="AM23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN23" t="n">
         <v>30</v>
@@ -4673,7 +4673,7 @@
         <v>1</v>
       </c>
       <c r="AS23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT23" t="n">
         <v>7</v>
@@ -4685,22 +4685,22 @@
         <v>5</v>
       </c>
       <c r="AW23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX23" t="n">
         <v>30</v>
       </c>
       <c r="AY23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ23" t="n">
         <v>1</v>
       </c>
       <c r="BA23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC23" t="n">
         <v>28</v>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -4813,25 +4813,25 @@
         <v>1</v>
       </c>
       <c r="AE24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG24" t="n">
         <v>7</v>
       </c>
-      <c r="AG24" t="n">
-        <v>6</v>
-      </c>
       <c r="AH24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AI24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL24" t="n">
         <v>21</v>
@@ -4843,13 +4843,13 @@
         <v>17</v>
       </c>
       <c r="AO24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AQ24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR24" t="n">
         <v>16</v>
@@ -4867,25 +4867,25 @@
         <v>28</v>
       </c>
       <c r="AW24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX24" t="n">
         <v>1</v>
       </c>
       <c r="AY24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ24" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA24" t="n">
         <v>10</v>
       </c>
       <c r="BB24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BC24" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -4992,16 +4992,16 @@
         <v>3.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE25" t="n">
         <v>10</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AG25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH25" t="n">
         <v>4</v>
@@ -5013,16 +5013,16 @@
         <v>26</v>
       </c>
       <c r="AK25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM25" t="n">
         <v>8</v>
       </c>
       <c r="AN25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO25" t="n">
         <v>21</v>
@@ -5040,7 +5040,7 @@
         <v>18</v>
       </c>
       <c r="AT25" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AU25" t="n">
         <v>9</v>
@@ -5058,16 +5058,16 @@
         <v>2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BA25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB25" t="n">
         <v>17</v>
       </c>
       <c r="BC25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -5174,19 +5174,19 @@
         <v>0.5</v>
       </c>
       <c r="AD26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF26" t="n">
         <v>8</v>
       </c>
-      <c r="AE26" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>7</v>
-      </c>
       <c r="AG26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI26" t="n">
         <v>16</v>
@@ -5204,13 +5204,13 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO26" t="n">
         <v>7</v>
       </c>
       <c r="AP26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ26" t="n">
         <v>4</v>
@@ -5237,16 +5237,16 @@
         <v>18</v>
       </c>
       <c r="AY26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA26" t="n">
         <v>14</v>
       </c>
       <c r="BB26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC26" t="n">
         <v>13</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -5278,157 +5278,157 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E27" t="n">
         <v>5</v>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.357</v>
+        <v>0.385</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>41.7</v>
+        <v>41.3</v>
       </c>
       <c r="J27" t="n">
-        <v>87.90000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="K27" t="n">
-        <v>0.474</v>
+        <v>0.471</v>
       </c>
       <c r="L27" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="M27" t="n">
-        <v>31.6</v>
+        <v>31</v>
       </c>
       <c r="N27" t="n">
-        <v>0.369</v>
+        <v>0.372</v>
       </c>
       <c r="O27" t="n">
-        <v>19.2</v>
+        <v>19.5</v>
       </c>
       <c r="P27" t="n">
-        <v>26.4</v>
+        <v>27</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.729</v>
+        <v>0.721</v>
       </c>
       <c r="R27" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="S27" t="n">
-        <v>32.4</v>
+        <v>32.9</v>
       </c>
       <c r="T27" t="n">
-        <v>42.4</v>
+        <v>43.1</v>
       </c>
       <c r="U27" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="V27" t="n">
-        <v>13.9</v>
+        <v>14.2</v>
       </c>
       <c r="W27" t="n">
         <v>6.1</v>
       </c>
       <c r="X27" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.2</v>
+        <v>21.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>114.3</v>
+        <v>113.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG27" t="n">
         <v>21</v>
       </c>
-      <c r="AF27" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>26</v>
-      </c>
       <c r="AH27" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AJ27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL27" t="n">
         <v>23</v>
       </c>
       <c r="AM27" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ27" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AR27" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS27" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AT27" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AU27" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AV27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW27" t="n">
         <v>28</v>
       </c>
       <c r="AX27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB27" t="n">
         <v>11</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>9</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -5538,22 +5538,22 @@
         <v>-0.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>10</v>
       </c>
       <c r="AF28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AG28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ28" t="n">
         <v>1</v>
@@ -5565,7 +5565,7 @@
         <v>25</v>
       </c>
       <c r="AM28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN28" t="n">
         <v>15</v>
@@ -5583,22 +5583,22 @@
         <v>17</v>
       </c>
       <c r="AS28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT28" t="n">
         <v>7</v>
       </c>
       <c r="AU28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV28" t="n">
         <v>1</v>
       </c>
       <c r="AW28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX28" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AY28" t="n">
         <v>29</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -5720,16 +5720,16 @@
         <v>-0.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF29" t="n">
         <v>23</v>
       </c>
       <c r="AG29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH29" t="n">
         <v>19</v>
@@ -5750,16 +5750,16 @@
         <v>1</v>
       </c>
       <c r="AN29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR29" t="n">
         <v>18</v>
@@ -5774,13 +5774,13 @@
         <v>17</v>
       </c>
       <c r="AV29" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY29" t="n">
         <v>28</v>
@@ -5789,10 +5789,10 @@
         <v>28</v>
       </c>
       <c r="BA29" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC29" t="n">
         <v>16</v>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -5824,103 +5824,103 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" t="n">
         <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="J30" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K30" t="n">
-        <v>0.462</v>
+        <v>0.458</v>
       </c>
       <c r="L30" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="M30" t="n">
-        <v>40.7</v>
+        <v>41</v>
       </c>
       <c r="N30" t="n">
-        <v>0.397</v>
+        <v>0.396</v>
       </c>
       <c r="O30" t="n">
-        <v>13.2</v>
+        <v>12.9</v>
       </c>
       <c r="P30" t="n">
-        <v>19.2</v>
+        <v>18.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.701</v>
       </c>
       <c r="R30" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="S30" t="n">
-        <v>38.2</v>
+        <v>38.9</v>
       </c>
       <c r="T30" t="n">
-        <v>49.3</v>
+        <v>50.4</v>
       </c>
       <c r="U30" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V30" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="W30" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="X30" t="n">
         <v>5.8</v>
       </c>
       <c r="Y30" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="AB30" t="n">
-        <v>110.5</v>
+        <v>110.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AE30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF30" t="n">
         <v>3</v>
       </c>
-      <c r="AF30" t="n">
-        <v>2</v>
-      </c>
       <c r="AG30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AH30" t="n">
         <v>19</v>
       </c>
       <c r="AI30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ30" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AK30" t="n">
         <v>15</v>
@@ -5932,7 +5932,7 @@
         <v>3</v>
       </c>
       <c r="AN30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO30" t="n">
         <v>30</v>
@@ -5944,7 +5944,7 @@
         <v>29</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AS30" t="n">
         <v>1</v>
@@ -5953,10 +5953,10 @@
         <v>1</v>
       </c>
       <c r="AU30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV30" t="n">
         <v>23</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>22</v>
       </c>
       <c r="AW30" t="n">
         <v>29</v>
@@ -5968,10 +5968,10 @@
         <v>12</v>
       </c>
       <c r="AZ30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB30" t="n">
         <v>16</v>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
         <v>-0.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6111,31 +6111,31 @@
         <v>14</v>
       </c>
       <c r="AM31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AN31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO31" t="n">
         <v>2</v>
       </c>
       <c r="AP31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR31" t="n">
         <v>21</v>
       </c>
       <c r="AS31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AU31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV31" t="n">
         <v>6</v>
@@ -6147,7 +6147,7 @@
         <v>29</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
         <v>30</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-17-2020-21</t>
+          <t>2021-01-17</t>
         </is>
       </c>
     </row>
